--- a/Final_Stores_Data.xlsx
+++ b/Final_Stores_Data.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="نتائج البحث العميقة" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="اشتراك ادوبي " state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="343">
   <si>
     <t>اسم المتجر</t>
   </si>
@@ -779,6 +780,267 @@
   </si>
   <si>
     <t>https://mahally.com/stores/2017176169/</t>
+  </si>
+  <si>
+    <t>https://ionetag.com/adobe-creative-cloud-1year/p730565343?srsltid=AfmBOooTdaL2vjFZhyWdV5J1k5VoJbix_R4HEgx_yEsCx4RSLq-oLQF6</t>
+  </si>
+  <si>
+    <t>ديجيتال ويف | Digital Wave</t>
+  </si>
+  <si>
+    <t>https://digitalwavestoree.com/?srsltid=AfmBOoqz2Qpg3v46Qu4Vs9yDzv8BQ_f_-2kwdQwiWHdAJ_T8Qx1QJ1wM</t>
+  </si>
+  <si>
+    <t>966531625366</t>
+  </si>
+  <si>
+    <t>منصة لينك اب | linkup.sa</t>
+  </si>
+  <si>
+    <t>https://linkup-sa.com/</t>
+  </si>
+  <si>
+    <t>966570262050</t>
+  </si>
+  <si>
+    <t>فايف ستور</t>
+  </si>
+  <si>
+    <t>https://stotre5.com/about-us/page-553469496</t>
+  </si>
+  <si>
+    <t>support@stotre5.com</t>
+  </si>
+  <si>
+    <t>966534937402</t>
+  </si>
+  <si>
+    <t>متجر سبيشل ستور</t>
+  </si>
+  <si>
+    <t>https://specialstoree.com/adobe-creative-cloud-1-month/p1944697836?srsltid=AfmBOorTBGYczw5M5RDYH6zC27Y4Aq_Dq4kd7X657GuJMdypa0z73MWL</t>
+  </si>
+  <si>
+    <t>551182468</t>
+  </si>
+  <si>
+    <t>متجر فنمك</t>
+  </si>
+  <si>
+    <t>https://www.adobe.com/eg_ar/creativecloud/plans.html</t>
+  </si>
+  <si>
+    <t>متجر S1</t>
+  </si>
+  <si>
+    <t>https://s1-stores.com/adobe-creative-cloud/p263951883</t>
+  </si>
+  <si>
+    <t>+966548245886</t>
+  </si>
+  <si>
+    <t>كريزى كى متجرك الموثوق لشراء كودك الرقمي</t>
+  </si>
+  <si>
+    <t>https://crezykey.com/ar</t>
+  </si>
+  <si>
+    <t>https://ar-saudita.com/%D8%A7%D8%B4%D8%AA%D8%B1%D8%A7%D9%83-%D8%A7%D8%AF%D9%88%D8%A8%D9%8A-%D9%83%D8%B1%D9%8A%D8%AA%D9%8A%D9%81-%D9%83%D9%84%D8%A7%D9%88%D8%AF-%D8%A7%D8%B4%D8%AA%D8%B1%D8%A7%D9%83-%D9%84%D9%85%D8%AF%D8%A9-%D8%B4%D9%87%D8%B1/p1972431649</t>
+  </si>
+  <si>
+    <t>متجر إيكو ستور | Echo Store</t>
+  </si>
+  <si>
+    <t>https://myechostores.com/</t>
+  </si>
+  <si>
+    <t>Goatsub 🐐 | قوت سوب</t>
+  </si>
+  <si>
+    <t>https://goatsub.com/</t>
+  </si>
+  <si>
+    <t>مدار | للمنتجات الرقمية</t>
+  </si>
+  <si>
+    <t>https://salla.sa/passkey/NKlemyG</t>
+  </si>
+  <si>
+    <t>+966501927715</t>
+  </si>
+  <si>
+    <t>متجر المفتاح الرقمي</t>
+  </si>
+  <si>
+    <t>https://digitalkeytech.com/adobe6month/p962052518</t>
+  </si>
+  <si>
+    <t>966559678552</t>
+  </si>
+  <si>
+    <t>سوفت وير تك</t>
+  </si>
+  <si>
+    <t>https://softwareteck.com/ar/%D8%A7%D8%B4%D8%AA%D8%B1%D8%A7%D9%83-%D8%A3%D8%AF%D9%88%D8%A8%D9%8A-%D9%83%D8%B1%D9%8A%D8%AA%D9%8A%D9%81-%D9%83%D9%84%D8%A7%D9%88%D8%AF-%D8%B3%D9%86%D9%87/p1381126323</t>
+  </si>
+  <si>
+    <t>+966566072124</t>
+  </si>
+  <si>
+    <t>سعد ستور</t>
+  </si>
+  <si>
+    <t>https://x.com/dieayaplus</t>
+  </si>
+  <si>
+    <t>0587146655</t>
+  </si>
+  <si>
+    <t>الكود النشط</t>
+  </si>
+  <si>
+    <t>https://codeekey.com/</t>
+  </si>
+  <si>
+    <t>لينكد ماستر Linked Master</t>
+  </si>
+  <si>
+    <t>https://salla.sa/linkdmaster</t>
+  </si>
+  <si>
+    <t>XB Core</t>
+  </si>
+  <si>
+    <t>https://xb-core.com/</t>
+  </si>
+  <si>
+    <t>966504919569</t>
+  </si>
+  <si>
+    <t>Digital Plus</t>
+  </si>
+  <si>
+    <t>https://digital-plus3.com/products/adobe12?srsltid=AfmBOor6UjUNBH4rtyRbgzII8QVpBQxRad-cD1fIWDnzIUuwpnQoHXkR</t>
+  </si>
+  <si>
+    <t>info@digital-plus3.com</t>
+  </si>
+  <si>
+    <t>+962795580312</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/direct/new</t>
+  </si>
+  <si>
+    <t>Q Keys</t>
+  </si>
+  <si>
+    <t>https://q--keys.com/en/</t>
+  </si>
+  <si>
+    <t>Cyber Card</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/discover/tech-cards-%D9%85%D9%88%D9%82%D8%B9</t>
+  </si>
+  <si>
+    <t>ترو بلس</t>
+  </si>
+  <si>
+    <t>https://supermarket.kanbkam.com/sa/ar/1-superhero-cake-topper-birthday-cupcake-toppers-decorations-party-supplies-for-fans-of-super-hero-B081PZZMVK</t>
+  </si>
+  <si>
+    <t>0587044534</t>
+  </si>
+  <si>
+    <t>خطاب للمنتجات الرقمية</t>
+  </si>
+  <si>
+    <t>https://salla.sa/passkey/mQPAXgV</t>
+  </si>
+  <si>
+    <t>متجر ثيربانتس</t>
+  </si>
+  <si>
+    <t>https://key-stores.com/ar/%D8%A3%D8%AF%D9%88%D8%A8%D9%8A-%D9%83%D8%B1%D9%8A%D8%AA%D9%8A%D9%81-%D9%83%D9%84%D8%A7%D9%88%D8%AF-%D9%84%D9%85%D8%AF%D8%A9-%D8%B4%D9%87%D8%B1-adobe-creative-cloud/p1812989301</t>
+  </si>
+  <si>
+    <t>966554795632</t>
+  </si>
+  <si>
+    <t>Passkey</t>
+  </si>
+  <si>
+    <t>https://salla.sa/passkey/DpZDpRY</t>
+  </si>
+  <si>
+    <t>بطاقة ستور</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/discover/%D8%A8%D8%B7%D8%A7%D9%82%D8%A7%D8%AA%C2%A0%D8%B1%D9%82%D9%85%D9%8A%D8%A9%C2%A0%D9%85%D9%86%C2%A0%D8%B3%D9%84%D8%A9</t>
+  </si>
+  <si>
+    <t>متجر اكتيف كيز</t>
+  </si>
+  <si>
+    <t>https://actvkeys.com/%D8%A3%D8%AF%D9%88%D8%A8%D9%8A-%D9%83%D8%B1%D9%8A%D9%8A%D8%AA%D9%81-%D9%83%D9%84%D8%A7%D9%88%D8%AF-adobe-creative-cloud/p1328979781</t>
+  </si>
+  <si>
+    <t>متجر كودكس</t>
+  </si>
+  <si>
+    <t>https://salla.sa/ccodex</t>
+  </si>
+  <si>
+    <t>966552819456</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/codextik</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@codextik</t>
+  </si>
+  <si>
+    <t>المفتاح الأصلي</t>
+  </si>
+  <si>
+    <t>https://www.noon.com/saudi-ar/high-end-car-key-cover-suitable-for-the-original-key-covers-of-mercedes-benz-models-gle-gla-c200l-c260l-and-e300l/ZF9495AB05088C65167FEZ/p/</t>
+  </si>
+  <si>
+    <t>D7E CODE</t>
+  </si>
+  <si>
+    <t>https://d7ecode.com/adobe-character-animator-subscription/p1449016369?srsltid=AfmBOoqR7YDOTXKUtT0Gbw1GcD8tPUpnNW_DAJXdtnkrFM2kKKzZgJpO</t>
+  </si>
+  <si>
+    <t>144901636</t>
+  </si>
+  <si>
+    <t>uplink-ksa</t>
+  </si>
+  <si>
+    <t>https://uplink-ksa.com/%D8%AD%D8%B3%D8%A7%D8%A8-%D8%A7%D8%AF%D9%88%D8%A8%D9%8A/p2106312480</t>
+  </si>
+  <si>
+    <t>966580930391</t>
+  </si>
+  <si>
+    <t>سبيشل ستور</t>
+  </si>
+  <si>
+    <t>https://special3-store.com/ar/%D8%A7%D8%B4%D8%AA%D8%B1%D8%A7%D9%83-%D8%A7%D8%AF%D9%88%D8%A8%D9%8A-%D9%83%D8%B1%D9%8A%D9%8A%D8%AA%D9%81-%D9%83%D9%84%D8%A7%D9%88%D8%AF-%D8%B4%D9%87%D8%B1/p361663597</t>
+  </si>
+  <si>
+    <t>966532650025</t>
+  </si>
+  <si>
+    <t>فاندر | Vandar</t>
+  </si>
+  <si>
+    <t>https://salla.sa/Vandar/product-descriptions/c1841184325</t>
+  </si>
+  <si>
+    <t>https://salla.sa/rqmistoresa.com/%D8%A7%D8%B4%D8%AA%D8%B1%D8%A7%D9%83-adobe-animate-%D8%AA%D8%B5%D9%85%D9%8A%D9%85-%D8%A7%D9%84%D8%B1%D8%B3%D9%88%D9%85-%D8%A7%D9%84%D9%85%D8%AA%D8%AD%D8%B1%D9%83%D8%A9/p796776109</t>
   </si>
 </sst>
 </file>
@@ -2861,6 +3123,960 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>274</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>250</v>
+      </c>
+      <c r="B10" t="s">
+        <v>277</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" t="s">
+        <v>283</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>284</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>285</v>
+      </c>
+      <c r="B14" t="s">
+        <v>286</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>287</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>288</v>
+      </c>
+      <c r="B15" t="s">
+        <v>289</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>290</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>291</v>
+      </c>
+      <c r="B16" t="s">
+        <v>292</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B17" t="s">
+        <v>295</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>296</v>
+      </c>
+      <c r="B18" t="s">
+        <v>297</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>298</v>
+      </c>
+      <c r="B19" t="s">
+        <v>299</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>300</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>301</v>
+      </c>
+      <c r="B20" t="s">
+        <v>302</v>
+      </c>
+      <c r="C20" t="s">
+        <v>303</v>
+      </c>
+      <c r="D20" t="s">
+        <v>304</v>
+      </c>
+      <c r="E20" t="s">
+        <v>305</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>306</v>
+      </c>
+      <c r="B21" t="s">
+        <v>307</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>308</v>
+      </c>
+      <c r="B22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>310</v>
+      </c>
+      <c r="B24" t="s">
+        <v>311</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>312</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>313</v>
+      </c>
+      <c r="B25" t="s">
+        <v>314</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>284</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>315</v>
+      </c>
+      <c r="B26" t="s">
+        <v>316</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>317</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>318</v>
+      </c>
+      <c r="B27" t="s">
+        <v>319</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>284</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>320</v>
+      </c>
+      <c r="B28" t="s">
+        <v>321</v>
+      </c>
+      <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>113</v>
+      </c>
+      <c r="G28" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>322</v>
+      </c>
+      <c r="B29" t="s">
+        <v>323</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>324</v>
+      </c>
+      <c r="B30" t="s">
+        <v>325</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>326</v>
+      </c>
+      <c r="E30" t="s">
+        <v>327</v>
+      </c>
+      <c r="F30" t="s">
+        <v>328</v>
+      </c>
+      <c r="G30" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>329</v>
+      </c>
+      <c r="B31" t="s">
+        <v>330</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>331</v>
+      </c>
+      <c r="B32" t="s">
+        <v>332</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>333</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>334</v>
+      </c>
+      <c r="B33" t="s">
+        <v>335</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>336</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>337</v>
+      </c>
+      <c r="B34" t="s">
+        <v>338</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>339</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>340</v>
+      </c>
+      <c r="B35" t="s">
+        <v>341</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36" t="s">
+        <v>342</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>183</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>